--- a/utils/monday_sprint_sprint_2024-47.xlsx
+++ b/utils/monday_sprint_sprint_2024-47.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="904" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="905" uniqueCount="160">
   <si>
     <t>Ticket</t>
   </si>
@@ -198,7 +198,7 @@
     <t>22/08/2024</t>
   </si>
   <si>
-    <t>10/03/2026</t>
+    <t>05/03/2026</t>
   </si>
   <si>
     <t>Semana 4</t>
@@ -3720,10 +3720,10 @@
         <v>40</v>
       </c>
       <c r="P10" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="Q10">
-        <v>36</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="4:17" x14ac:dyDescent="0.25">
@@ -3752,10 +3752,10 @@
         <v>11</v>
       </c>
       <c r="P11" t="s">
-        <v>85</v>
+        <v>21</v>
       </c>
       <c r="Q11">
-        <v>3</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12" spans="7:17" x14ac:dyDescent="0.25">
@@ -3772,13 +3772,13 @@
         <v>0</v>
       </c>
       <c r="P12" t="s">
-        <v>43</v>
+        <v>85</v>
       </c>
       <c r="Q12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="7:14" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="7:17" x14ac:dyDescent="0.25">
       <c r="G13" t="s">
         <v>153</v>
       </c>
@@ -3790,6 +3790,12 @@
       </c>
       <c r="N13">
         <v>7</v>
+      </c>
+      <c r="P13" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q13">
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="7:14" x14ac:dyDescent="0.25">
@@ -3857,7 +3863,7 @@
         <v>15</v>
       </c>
       <c r="F21" s="2">
-        <v>551</v>
+        <v>546</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>56</v>

--- a/utils/monday_sprint_sprint_2024-47.xlsx
+++ b/utils/monday_sprint_sprint_2024-47.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="965" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="964" uniqueCount="196">
   <si>
     <t>Ticket</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Equipe TI</t>
   </si>
   <si>
-    <t>Entrada Sprint</t>
+    <t>Abertura</t>
   </si>
   <si>
     <t>Encerramento</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>SLA (15 dias)</t>
+    <t>Dentro da SLA</t>
   </si>
   <si>
     <t>Semana</t>
@@ -60,7 +60,7 @@
     <t>Mês</t>
   </si>
   <si>
-    <t>28295</t>
+    <t>7618237566</t>
   </si>
   <si>
     <t>Setor não informado</t>
@@ -87,7 +87,7 @@
     <t>11/10/2024</t>
   </si>
   <si>
-    <t>N/A</t>
+    <t>28/10/2024</t>
   </si>
   <si>
     <t>Feito</t>
@@ -102,7 +102,7 @@
     <t>Outubro</t>
   </si>
   <si>
-    <t>27180</t>
+    <t>7624210581</t>
   </si>
   <si>
     <t>Projeto</t>
@@ -120,10 +120,7 @@
     <t>A fazer</t>
   </si>
   <si>
-    <t>Aberto</t>
-  </si>
-  <si>
-    <t>26830</t>
+    <t>7539127189</t>
   </si>
   <si>
     <t>Segregação custeiro - Acabamento - Apoio industrial</t>
@@ -135,40 +132,55 @@
     <t>Semana 1</t>
   </si>
   <si>
-    <t>28251</t>
+    <t>7618395308</t>
   </si>
   <si>
     <t>Data MPS Usin</t>
   </si>
   <si>
+    <t>24/10/2024</t>
+  </si>
+  <si>
+    <t>7539127173</t>
+  </si>
+  <si>
     <t>Segregação custeiro - Acabamento - Rebarbação</t>
   </si>
   <si>
-    <t>28225</t>
+    <t>7618478729</t>
   </si>
   <si>
     <t>Ajuste Tempo estimado sistema Invoice</t>
   </si>
   <si>
-    <t>28262</t>
+    <t>7618612232</t>
   </si>
   <si>
     <t>Revisão de PDI’s:</t>
   </si>
   <si>
+    <t>17/10/2024</t>
+  </si>
+  <si>
     <t>Fazendo</t>
   </si>
   <si>
-    <t>28162</t>
+    <t>7618665601</t>
   </si>
   <si>
     <t>Liberação de Embarque com Divergencia</t>
   </si>
   <si>
+    <t>20/10/2024</t>
+  </si>
+  <si>
+    <t>7618612908</t>
+  </si>
+  <si>
     <t>Preenchimento dos PDI’s</t>
   </si>
   <si>
-    <t>27808</t>
+    <t>7529338786</t>
   </si>
   <si>
     <t>Ajustes no sistema de ensaios destrutivos de peças seriadas</t>
@@ -183,19 +195,28 @@
     <t>Setembro</t>
   </si>
   <si>
+    <t>7618614031</t>
+  </si>
+  <si>
     <t>Preenchimento das cotas</t>
   </si>
   <si>
-    <t>28348</t>
+    <t>7617189670</t>
   </si>
   <si>
     <t>Alterações Sistema Indicadores GIQ - Melhorar Legenda</t>
   </si>
   <si>
+    <t>23/10/2024</t>
+  </si>
+  <si>
+    <t>7618613398</t>
+  </si>
+  <si>
     <t>Consulta de PDI’s preenchidos</t>
   </si>
   <si>
-    <t>25807</t>
+    <t>7626973004</t>
   </si>
   <si>
     <t>Sistema para Faseamento de Vendas e Faturamento / Manutenção dos dados importados (copy)</t>
@@ -204,91 +225,118 @@
     <t>14/10/2024</t>
   </si>
   <si>
+    <t>7539127151</t>
+  </si>
+  <si>
     <t>Segregação custeiro - Acabamento - Tratamento térmico</t>
   </si>
   <si>
+    <t>7617208129</t>
+  </si>
+  <si>
     <t>Alterações Sistema Indicadores GIQ - Diferenciar itens abaixo da meta com e sem plano de ação</t>
   </si>
   <si>
+    <t>7617233784</t>
+  </si>
+  <si>
     <t>Alterações Sistema Indicadores GIQ - Página inicial - Disponibilizar filtro/opções para alterar o setor dos gráficos</t>
   </si>
   <si>
+    <t>7617229321</t>
+  </si>
+  <si>
     <t>Alterações Sistema Indicadores GIQ - Página Inicial -  Disponibilizar gráficos na página inicial de acordo com a área do usuário logado,</t>
   </si>
   <si>
-    <t>27561</t>
-  </si>
-  <si>
-    <t>Solicitação de serviço</t>
+    <t>7618572398</t>
   </si>
   <si>
     <t>Abertura de Chamado - Criação de Cadastro de Calendário de Máquina para Cálculo de IROG</t>
   </si>
   <si>
-    <t>Solicito a abertura de chamado para criação de tela de cadastro no sistema que possibilite a criação de calendário de máquinas para cálculo de IROG, segue abaixo modelo utilizado no EFACT: Conforme acordado em reunião (22/08) é necessário que haja uma funcionalidade no calendário que permita que o c</t>
-  </si>
-  <si>
-    <t>Guilherme Mendes</t>
-  </si>
-  <si>
-    <t>Sistemas</t>
-  </si>
-  <si>
-    <t>05/03/2026</t>
+    <t>7617212374</t>
   </si>
   <si>
     <t>Alterações Sistema Indicadores GIQ - Verificar a possibilidade de incluir o número do plano de ação quando houver</t>
   </si>
   <si>
-    <t>27886</t>
+    <t>7627215624</t>
   </si>
   <si>
     <t>Registro de inspeção</t>
   </si>
   <si>
+    <t>7617242029</t>
+  </si>
+  <si>
     <t>Alterações Sistema Indicadores GIQ - Página inicial - Ao clicar no nome do indicador levar para o gráfico correspondente</t>
   </si>
   <si>
+    <t>7618615499</t>
+  </si>
+  <si>
     <t>Consulta para Engenharia</t>
   </si>
   <si>
+    <t>21/10/2024</t>
+  </si>
+  <si>
+    <t>7617265611</t>
+  </si>
+  <si>
     <t>Alterações Sistema Indicadores GIQ - Página inicial - Adicionar Descrição do Problema (campo “principais problemas” da planilha do plano de ação atual) entre Critérios de Medição e Descrição da Ação</t>
   </si>
   <si>
+    <t>7617245371</t>
+  </si>
+  <si>
     <t>Alterações Sistema Indicadores GIQ - Página inicial - incluir sinaleiro de acordo com o resultado do indicador no acumulado do ano</t>
   </si>
   <si>
+    <t>7617283273</t>
+  </si>
+  <si>
     <t>Alterações Sistema Indicadores GIQ - Página inicial - Incluir campo para percentual de conclusão do plano de ação</t>
   </si>
   <si>
+    <t>7617270475</t>
+  </si>
+  <si>
     <t>Alterações Sistema Indicadores GIQ - Página inicial -  Incluir campo com a data de criação do plano de ação (não editável)</t>
   </si>
   <si>
+    <t>7618614470</t>
+  </si>
+  <si>
     <t>Consulta para Inspetores</t>
   </si>
   <si>
+    <t>7618616027</t>
+  </si>
+  <si>
     <t>Preenchimento do PDI</t>
   </si>
   <si>
-    <t>28316</t>
+    <t>7618192660</t>
   </si>
   <si>
     <t>TAMPAS</t>
   </si>
   <si>
-    <t>28139</t>
+    <t>7618733104</t>
   </si>
   <si>
     <t>Dados Alea</t>
   </si>
   <si>
-    <t>25032</t>
+    <t>7619778747</t>
   </si>
   <si>
     <t>Agendar serviço para carga da base de programação para o APP</t>
   </si>
   <si>
-    <t>28135</t>
+    <t>7522246499</t>
   </si>
   <si>
     <t>Apontamento de moldagem USE - Máquina</t>
@@ -297,148 +345,169 @@
     <t>27/09/2024</t>
   </si>
   <si>
+    <t>15/10/2024</t>
+  </si>
+  <si>
     <t>Semana 4</t>
   </si>
   <si>
+    <t>7617221133</t>
+  </si>
+  <si>
     <t>Alterações Sistema Indicadores GIQ  Usar cores menos berrantes</t>
   </si>
   <si>
+    <t>7654763484</t>
+  </si>
+  <si>
     <t>Criar controle no cadastro de senhas para esses campos</t>
   </si>
   <si>
-    <t>17/10/2024</t>
-  </si>
-  <si>
     <t>Semana 3</t>
   </si>
   <si>
+    <t>7654768061</t>
+  </si>
+  <si>
     <t>Sérgio pediu para que esses campos fiquem registrados no log</t>
   </si>
   <si>
+    <t>7654772616</t>
+  </si>
+  <si>
     <t>Criar uma nova tabela dentro do cpp para se ter a estrutura do conjunto</t>
   </si>
   <si>
-    <t>28300</t>
+    <t>7618221577</t>
   </si>
   <si>
     <t>Irog ajustagem</t>
   </si>
   <si>
-    <t>28329</t>
+    <t>26/10/2024</t>
+  </si>
+  <si>
+    <t>7617307848</t>
   </si>
   <si>
     <t>Utilização dos Apontamentos Moldagem ULE para Custeio</t>
   </si>
   <si>
-    <t>28280</t>
+    <t>7618295960</t>
   </si>
   <si>
     <t>Acesso Limitado Sistema</t>
   </si>
   <si>
-    <t>28306</t>
+    <t>7618211784</t>
   </si>
   <si>
     <t>Emissão de Nota Fiscal - Setor 7102 (Serviços com Terceiros)</t>
   </si>
   <si>
-    <t>28322</t>
+    <t>7618178641</t>
   </si>
   <si>
     <t>AUMENTO DE CARACTERES</t>
   </si>
   <si>
-    <t>28349</t>
+    <t>7617178657</t>
   </si>
   <si>
     <t>Inventti - Campos cBenef</t>
   </si>
   <si>
-    <t>28255</t>
+    <t>7618353775</t>
   </si>
   <si>
     <t>[NIMBI] Ajustes na API de material + Criação da rotina que inclui/inativa/atualiza cadastro dos materiais no</t>
   </si>
   <si>
-    <t>28216</t>
+    <t>7618524265</t>
   </si>
   <si>
     <t>Ordenação de Recibos de Embarque</t>
   </si>
   <si>
-    <t>28254</t>
+    <t>7618368360</t>
   </si>
   <si>
     <t>Sistema de Custeio - Peças Grupo de Liga 0 (Zero)</t>
   </si>
   <si>
-    <t>28200</t>
+    <t>7618541059</t>
   </si>
   <si>
     <t>Melhoria no módulo da Portaria</t>
   </si>
   <si>
-    <t>28224</t>
+    <t>7618490951</t>
   </si>
   <si>
     <t>Data CPC - Planilhão pré produtivo</t>
   </si>
   <si>
-    <t>28239</t>
+    <t>7618421746</t>
   </si>
   <si>
     <t>Dificuldade de apontamento - Komatsu</t>
   </si>
   <si>
-    <t>28235</t>
+    <t>7618438654</t>
   </si>
   <si>
     <t>Alterar filtro relatório seq. sem atividade complementar</t>
   </si>
   <si>
-    <t>28227</t>
+    <t>7618457602</t>
   </si>
   <si>
     <t>[NIMBI] Criação da rotina que integra a requisições emitidas no Nimbi a cada 5 min</t>
   </si>
   <si>
-    <t>28274</t>
+    <t>7618315738</t>
   </si>
   <si>
     <t>Adicionar campo na tela de corrida</t>
   </si>
   <si>
-    <t>28330</t>
+    <t>16/10/2024</t>
+  </si>
+  <si>
+    <t>7617296234</t>
   </si>
   <si>
     <t>Contabilização DIFA</t>
   </si>
   <si>
-    <t>6090</t>
+    <t>7529338693</t>
   </si>
   <si>
     <t>Analisar as demandas do fluxo de revisão de documentos</t>
   </si>
   <si>
-    <t>28147</t>
+    <t>7618721079</t>
   </si>
   <si>
     <t>PESO ITEM COMERCIAL</t>
   </si>
   <si>
-    <t>28121</t>
+    <t>7627024794</t>
   </si>
   <si>
     <t>[NIMBI] Criação da rotina que integra os pedidos a cada 30 min</t>
   </si>
   <si>
-    <t>28025</t>
+    <t>7627215687</t>
   </si>
   <si>
     <t>Síntese de reunião - Projeto IROG - Matriz</t>
   </si>
   <si>
-    <t>28169</t>
+    <t>27/10/2024</t>
+  </si>
+  <si>
+    <t>7618563335</t>
   </si>
   <si>
     <t>Aba conclusão usinagem</t>
@@ -450,7 +519,7 @@
     <t>Período</t>
   </si>
   <si>
-    <t>SPRINT 2024-47</t>
+    <t>Set/2024</t>
   </si>
   <si>
     <t>Base</t>
@@ -1092,13 +1161,13 @@
         <v>33</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L3" s="2" t="s">
         <v>34</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="N3" s="2" t="s">
         <v>27</v>
@@ -1109,46 +1178,46 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J4" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>38</v>
-      </c>
       <c r="K4" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>34</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O4" s="2" t="s">
         <v>28</v>
@@ -1156,37 +1225,37 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K5" s="2" t="s">
         <v>41</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>24</v>
       </c>
       <c r="L5" s="2" t="s">
         <v>25</v>
@@ -1203,7 +1272,7 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>16</v>
@@ -1215,10 +1284,10 @@
         <v>18</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>20</v>
@@ -1230,19 +1299,19 @@
         <v>22</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>34</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O6" s="2" t="s">
         <v>28</v>
@@ -1250,7 +1319,7 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>16</v>
@@ -1262,10 +1331,10 @@
         <v>18</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>20</v>
@@ -1297,7 +1366,7 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>16</v>
@@ -1309,10 +1378,10 @@
         <v>18</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>20</v>
@@ -1327,13 +1396,13 @@
         <v>23</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="N8" s="2" t="s">
         <v>27</v>
@@ -1344,7 +1413,7 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>16</v>
@@ -1356,10 +1425,10 @@
         <v>18</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>20</v>
@@ -1374,7 +1443,7 @@
         <v>23</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="L9" s="2" t="s">
         <v>25</v>
@@ -1391,7 +1460,7 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>16</v>
@@ -1403,10 +1472,10 @@
         <v>18</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>20</v>
@@ -1421,13 +1490,13 @@
         <v>23</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="N10" s="2" t="s">
         <v>27</v>
@@ -1438,7 +1507,7 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>16</v>
@@ -1450,10 +1519,10 @@
         <v>18</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>20</v>
@@ -1465,27 +1534,27 @@
         <v>22</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L11" s="2" t="s">
         <v>34</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>16</v>
@@ -1497,10 +1566,10 @@
         <v>18</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>20</v>
@@ -1515,13 +1584,13 @@
         <v>23</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="N12" s="2" t="s">
         <v>27</v>
@@ -1532,7 +1601,7 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>16</v>
@@ -1544,10 +1613,10 @@
         <v>18</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>20</v>
@@ -1562,7 +1631,7 @@
         <v>23</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="L13" s="2" t="s">
         <v>25</v>
@@ -1579,7 +1648,7 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>16</v>
@@ -1591,10 +1660,10 @@
         <v>18</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>20</v>
@@ -1609,13 +1678,13 @@
         <v>23</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="N14" s="2" t="s">
         <v>27</v>
@@ -1626,7 +1695,7 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>16</v>
@@ -1638,10 +1707,10 @@
         <v>18</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>20</v>
@@ -1653,16 +1722,16 @@
         <v>22</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L15" s="2" t="s">
         <v>34</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="N15" s="2" t="s">
         <v>27</v>
@@ -1673,7 +1742,7 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>36</v>
+        <v>70</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>16</v>
@@ -1685,10 +1754,10 @@
         <v>18</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>20</v>
@@ -1700,19 +1769,19 @@
         <v>22</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L16" s="2" t="s">
         <v>34</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O16" s="2" t="s">
         <v>28</v>
@@ -1720,7 +1789,7 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>16</v>
@@ -1732,25 +1801,25 @@
         <v>18</v>
       </c>
       <c r="E17" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K17" s="2" t="s">
         <v>64</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K17" s="2" t="s">
-        <v>24</v>
       </c>
       <c r="L17" s="2" t="s">
         <v>25</v>
@@ -1767,7 +1836,7 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>16</v>
@@ -1779,10 +1848,10 @@
         <v>18</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>20</v>
@@ -1797,13 +1866,13 @@
         <v>23</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L18" s="2" t="s">
         <v>34</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="N18" s="2" t="s">
         <v>27</v>
@@ -1814,7 +1883,7 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>16</v>
@@ -1826,10 +1895,10 @@
         <v>18</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>20</v>
@@ -1844,13 +1913,13 @@
         <v>23</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L19" s="2" t="s">
         <v>34</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="N19" s="2" t="s">
         <v>27</v>
@@ -1861,7 +1930,7 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>16</v>
@@ -1870,28 +1939,28 @@
         <v>17</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>68</v>
+        <v>18</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>32</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>71</v>
+        <v>21</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>72</v>
+        <v>22</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>73</v>
+        <v>24</v>
       </c>
       <c r="L20" s="2" t="s">
         <v>25</v>
@@ -1908,7 +1977,7 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>57</v>
+        <v>80</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>16</v>
@@ -1920,10 +1989,10 @@
         <v>18</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>20</v>
@@ -1938,7 +2007,7 @@
         <v>23</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="L21" s="2" t="s">
         <v>25</v>
@@ -1955,7 +2024,7 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>16</v>
@@ -1967,10 +2036,10 @@
         <v>18</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>20</v>
@@ -1982,16 +2051,16 @@
         <v>22</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L22" s="2" t="s">
         <v>34</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="N22" s="2" t="s">
         <v>27</v>
@@ -2002,7 +2071,7 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>57</v>
+        <v>84</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>16</v>
@@ -2014,10 +2083,10 @@
         <v>18</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>20</v>
@@ -2032,13 +2101,13 @@
         <v>23</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="N23" s="2" t="s">
         <v>27</v>
@@ -2049,7 +2118,7 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>45</v>
+        <v>86</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>16</v>
@@ -2061,10 +2130,10 @@
         <v>18</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>20</v>
@@ -2079,7 +2148,7 @@
         <v>23</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>24</v>
+        <v>88</v>
       </c>
       <c r="L24" s="2" t="s">
         <v>25</v>
@@ -2096,7 +2165,7 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>57</v>
+        <v>89</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>16</v>
@@ -2108,10 +2177,10 @@
         <v>18</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>20</v>
@@ -2126,7 +2195,7 @@
         <v>23</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="L25" s="2" t="s">
         <v>25</v>
@@ -2143,7 +2212,7 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>57</v>
+        <v>91</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>16</v>
@@ -2155,10 +2224,10 @@
         <v>18</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>20</v>
@@ -2173,13 +2242,13 @@
         <v>23</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L26" s="2" t="s">
         <v>34</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="N26" s="2" t="s">
         <v>27</v>
@@ -2190,7 +2259,7 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>57</v>
+        <v>93</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>16</v>
@@ -2202,10 +2271,10 @@
         <v>18</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>20</v>
@@ -2220,7 +2289,7 @@
         <v>23</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="L27" s="2" t="s">
         <v>25</v>
@@ -2237,7 +2306,7 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>57</v>
+        <v>95</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>16</v>
@@ -2249,10 +2318,10 @@
         <v>18</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>20</v>
@@ -2267,7 +2336,7 @@
         <v>23</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="L28" s="2" t="s">
         <v>25</v>
@@ -2284,7 +2353,7 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>45</v>
+        <v>97</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>16</v>
@@ -2296,10 +2365,10 @@
         <v>18</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>20</v>
@@ -2314,7 +2383,7 @@
         <v>23</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>24</v>
+        <v>88</v>
       </c>
       <c r="L29" s="2" t="s">
         <v>25</v>
@@ -2331,7 +2400,7 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>45</v>
+        <v>99</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>16</v>
@@ -2343,10 +2412,10 @@
         <v>18</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>20</v>
@@ -2361,7 +2430,7 @@
         <v>23</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>24</v>
+        <v>88</v>
       </c>
       <c r="L30" s="2" t="s">
         <v>25</v>
@@ -2378,7 +2447,7 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>16</v>
@@ -2390,10 +2459,10 @@
         <v>18</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>20</v>
@@ -2408,13 +2477,13 @@
         <v>23</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L31" s="2" t="s">
         <v>34</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="N31" s="2" t="s">
         <v>27</v>
@@ -2425,7 +2494,7 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>16</v>
@@ -2437,10 +2506,10 @@
         <v>18</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>20</v>
@@ -2455,7 +2524,7 @@
         <v>23</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="L32" s="2" t="s">
         <v>25</v>
@@ -2472,7 +2541,7 @@
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>16</v>
@@ -2484,10 +2553,10 @@
         <v>18</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>20</v>
@@ -2502,13 +2571,13 @@
         <v>23</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="N33" s="2" t="s">
         <v>27</v>
@@ -2519,7 +2588,7 @@
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>16</v>
@@ -2531,10 +2600,10 @@
         <v>18</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>20</v>
@@ -2546,27 +2615,27 @@
         <v>22</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>93</v>
+        <v>109</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>24</v>
+        <v>110</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="O34" s="2" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>57</v>
+        <v>112</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>16</v>
@@ -2578,10 +2647,10 @@
         <v>18</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>95</v>
+        <v>113</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>95</v>
+        <v>113</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>20</v>
@@ -2596,7 +2665,7 @@
         <v>23</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="L35" s="2" t="s">
         <v>25</v>
@@ -2613,7 +2682,7 @@
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>85</v>
+        <v>114</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>16</v>
@@ -2625,10 +2694,10 @@
         <v>18</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>96</v>
+        <v>115</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>96</v>
+        <v>115</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>20</v>
@@ -2640,10 +2709,10 @@
         <v>22</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>97</v>
+        <v>48</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="L36" s="2" t="s">
         <v>25</v>
@@ -2652,7 +2721,7 @@
         <v>26</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>98</v>
+        <v>116</v>
       </c>
       <c r="O36" s="2" t="s">
         <v>28</v>
@@ -2660,7 +2729,7 @@
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>85</v>
+        <v>117</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>16</v>
@@ -2672,10 +2741,10 @@
         <v>18</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>99</v>
+        <v>118</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>99</v>
+        <v>118</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>20</v>
@@ -2687,10 +2756,10 @@
         <v>22</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>97</v>
+        <v>48</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="L37" s="2" t="s">
         <v>25</v>
@@ -2699,7 +2768,7 @@
         <v>26</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>98</v>
+        <v>116</v>
       </c>
       <c r="O37" s="2" t="s">
         <v>28</v>
@@ -2707,7 +2776,7 @@
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>85</v>
+        <v>119</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>16</v>
@@ -2719,10 +2788,10 @@
         <v>18</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>20</v>
@@ -2734,10 +2803,10 @@
         <v>22</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>97</v>
+        <v>48</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="L38" s="2" t="s">
         <v>25</v>
@@ -2746,7 +2815,7 @@
         <v>26</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>98</v>
+        <v>116</v>
       </c>
       <c r="O38" s="2" t="s">
         <v>28</v>
@@ -2754,7 +2823,7 @@
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>16</v>
@@ -2766,10 +2835,10 @@
         <v>18</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>102</v>
+        <v>122</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>102</v>
+        <v>122</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>20</v>
@@ -2784,7 +2853,7 @@
         <v>23</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>24</v>
+        <v>123</v>
       </c>
       <c r="L39" s="2" t="s">
         <v>25</v>
@@ -2801,7 +2870,7 @@
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>103</v>
+        <v>124</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>16</v>
@@ -2813,10 +2882,10 @@
         <v>18</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>104</v>
+        <v>125</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>104</v>
+        <v>125</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>20</v>
@@ -2831,7 +2900,7 @@
         <v>23</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="L40" s="2" t="s">
         <v>25</v>
@@ -2848,7 +2917,7 @@
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>105</v>
+        <v>126</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>16</v>
@@ -2860,10 +2929,10 @@
         <v>18</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>106</v>
+        <v>127</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>106</v>
+        <v>127</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>20</v>
@@ -2878,7 +2947,7 @@
         <v>23</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>24</v>
+        <v>110</v>
       </c>
       <c r="L41" s="2" t="s">
         <v>25</v>
@@ -2895,7 +2964,7 @@
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>16</v>
@@ -2907,10 +2976,10 @@
         <v>18</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>108</v>
+        <v>129</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>108</v>
+        <v>129</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>20</v>
@@ -2925,7 +2994,7 @@
         <v>23</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="L42" s="2" t="s">
         <v>25</v>
@@ -2942,7 +3011,7 @@
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>109</v>
+        <v>130</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>16</v>
@@ -2954,10 +3023,10 @@
         <v>18</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>110</v>
+        <v>131</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>110</v>
+        <v>131</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>20</v>
@@ -2972,7 +3041,7 @@
         <v>23</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="L43" s="2" t="s">
         <v>25</v>
@@ -2989,7 +3058,7 @@
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>111</v>
+        <v>132</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>16</v>
@@ -3001,10 +3070,10 @@
         <v>18</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>112</v>
+        <v>133</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>112</v>
+        <v>133</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>20</v>
@@ -3019,7 +3088,7 @@
         <v>23</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>24</v>
+        <v>110</v>
       </c>
       <c r="L44" s="2" t="s">
         <v>25</v>
@@ -3036,7 +3105,7 @@
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>113</v>
+        <v>134</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>16</v>
@@ -3048,10 +3117,10 @@
         <v>18</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>114</v>
+        <v>135</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>114</v>
+        <v>135</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>20</v>
@@ -3066,7 +3135,7 @@
         <v>23</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="L45" s="2" t="s">
         <v>25</v>
@@ -3083,7 +3152,7 @@
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>115</v>
+        <v>136</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>16</v>
@@ -3095,10 +3164,10 @@
         <v>18</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>116</v>
+        <v>137</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>116</v>
+        <v>137</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>20</v>
@@ -3113,7 +3182,7 @@
         <v>23</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="L46" s="2" t="s">
         <v>25</v>
@@ -3130,7 +3199,7 @@
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>117</v>
+        <v>138</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>16</v>
@@ -3142,10 +3211,10 @@
         <v>18</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>118</v>
+        <v>139</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>118</v>
+        <v>139</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>20</v>
@@ -3160,7 +3229,7 @@
         <v>23</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L47" s="2" t="s">
         <v>25</v>
@@ -3177,7 +3246,7 @@
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>119</v>
+        <v>140</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>16</v>
@@ -3189,10 +3258,10 @@
         <v>18</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>120</v>
+        <v>141</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>120</v>
+        <v>141</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>20</v>
@@ -3207,7 +3276,7 @@
         <v>23</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L48" s="2" t="s">
         <v>25</v>
@@ -3224,7 +3293,7 @@
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>121</v>
+        <v>142</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>16</v>
@@ -3236,10 +3305,10 @@
         <v>18</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>122</v>
+        <v>143</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>122</v>
+        <v>143</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>20</v>
@@ -3254,7 +3323,7 @@
         <v>23</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="L49" s="2" t="s">
         <v>25</v>
@@ -3271,37 +3340,37 @@
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="G50" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I50" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J50" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K50" s="2" t="s">
         <v>123</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="F50" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="G50" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H50" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I50" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J50" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K50" s="2" t="s">
-        <v>24</v>
       </c>
       <c r="L50" s="2" t="s">
         <v>25</v>
@@ -3318,7 +3387,7 @@
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>16</v>
@@ -3330,10 +3399,10 @@
         <v>18</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>126</v>
+        <v>147</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>126</v>
+        <v>147</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>20</v>
@@ -3348,7 +3417,7 @@
         <v>23</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>24</v>
+        <v>110</v>
       </c>
       <c r="L51" s="2" t="s">
         <v>25</v>
@@ -3365,7 +3434,7 @@
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>127</v>
+        <v>148</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>16</v>
@@ -3377,10 +3446,10 @@
         <v>18</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>128</v>
+        <v>149</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>128</v>
+        <v>149</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>20</v>
@@ -3395,7 +3464,7 @@
         <v>23</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="L52" s="2" t="s">
         <v>25</v>
@@ -3412,7 +3481,7 @@
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>129</v>
+        <v>150</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>16</v>
@@ -3424,10 +3493,10 @@
         <v>18</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>130</v>
+        <v>151</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>130</v>
+        <v>151</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>20</v>
@@ -3442,7 +3511,7 @@
         <v>23</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>24</v>
+        <v>152</v>
       </c>
       <c r="L53" s="2" t="s">
         <v>25</v>
@@ -3459,7 +3528,7 @@
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>131</v>
+        <v>153</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>16</v>
@@ -3471,10 +3540,10 @@
         <v>18</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>132</v>
+        <v>154</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>132</v>
+        <v>154</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>20</v>
@@ -3489,7 +3558,7 @@
         <v>23</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="L54" s="2" t="s">
         <v>25</v>
@@ -3506,7 +3575,7 @@
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>133</v>
+        <v>155</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>16</v>
@@ -3518,10 +3587,10 @@
         <v>18</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>134</v>
+        <v>156</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>134</v>
+        <v>156</v>
       </c>
       <c r="G55" s="2" t="s">
         <v>20</v>
@@ -3533,10 +3602,10 @@
         <v>22</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>24</v>
+        <v>123</v>
       </c>
       <c r="L55" s="2" t="s">
         <v>25</v>
@@ -3545,15 +3614,15 @@
         <v>26</v>
       </c>
       <c r="N55" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="O55" s="2" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>135</v>
+        <v>157</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>16</v>
@@ -3565,10 +3634,10 @@
         <v>18</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>136</v>
+        <v>158</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>136</v>
+        <v>158</v>
       </c>
       <c r="G56" s="2" t="s">
         <v>20</v>
@@ -3583,7 +3652,7 @@
         <v>23</v>
       </c>
       <c r="K56" s="2" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="L56" s="2" t="s">
         <v>25</v>
@@ -3600,7 +3669,7 @@
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>137</v>
+        <v>159</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>16</v>
@@ -3612,10 +3681,10 @@
         <v>18</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>138</v>
+        <v>160</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>138</v>
+        <v>160</v>
       </c>
       <c r="G57" s="2" t="s">
         <v>20</v>
@@ -3627,10 +3696,10 @@
         <v>22</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="K57" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="L57" s="2" t="s">
         <v>25</v>
@@ -3647,7 +3716,7 @@
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>139</v>
+        <v>161</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>16</v>
@@ -3659,10 +3728,10 @@
         <v>18</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>140</v>
+        <v>162</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>140</v>
+        <v>162</v>
       </c>
       <c r="G58" s="2" t="s">
         <v>20</v>
@@ -3674,10 +3743,10 @@
         <v>22</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>24</v>
+        <v>163</v>
       </c>
       <c r="L58" s="2" t="s">
         <v>25</v>
@@ -3694,7 +3763,7 @@
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>16</v>
@@ -3706,10 +3775,10 @@
         <v>18</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>142</v>
+        <v>165</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>142</v>
+        <v>165</v>
       </c>
       <c r="G59" s="2" t="s">
         <v>20</v>
@@ -3752,23 +3821,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>143</v>
+        <v>166</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>144</v>
+        <v>167</v>
       </c>
       <c r="B2" t="s">
-        <v>145</v>
+        <v>168</v>
       </c>
       <c r="D2" t="s">
-        <v>146</v>
+        <v>169</v>
       </c>
       <c r="E2" t="s">
-        <v>147</v>
+        <v>170</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -3776,16 +3845,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>148</v>
+        <v>171</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>149</v>
+        <v>172</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>150</v>
+        <v>173</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>151</v>
+        <v>174</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -3796,7 +3865,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="4">
-        <v>510</v>
+        <v>11.38</v>
       </c>
       <c r="J5" s="4">
         <v>1</v>
@@ -3804,7 +3873,7 @@
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>152</v>
+        <v>175</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
@@ -3817,7 +3886,7 @@
     </row>
     <row r="23" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J23" t="s">
-        <v>153</v>
+        <v>176</v>
       </c>
       <c r="K23">
         <v>0</v>
@@ -3825,7 +3894,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>154</v>
+        <v>177</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -3856,12 +3925,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>155</v>
+        <v>178</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>148</v>
+        <v>171</v>
       </c>
       <c r="B2">
         <v>58</v>
@@ -3875,7 +3944,7 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>510</v>
+        <v>11.38</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
@@ -3885,25 +3954,25 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>156</v>
+        <v>179</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>157</v>
+        <v>180</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>158</v>
+        <v>181</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>159</v>
+        <v>182</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>160</v>
+        <v>183</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>161</v>
+        <v>184</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -3920,13 +3989,13 @@
         <v>57</v>
       </c>
       <c r="G10" t="s">
-        <v>162</v>
+        <v>185</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>163</v>
+        <v>186</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -3938,10 +4007,10 @@
         <v>40</v>
       </c>
       <c r="P10" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="Q10">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="4:17" x14ac:dyDescent="0.25">
@@ -3961,7 +4030,7 @@
         <v>26</v>
       </c>
       <c r="K11">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="M11" t="s">
         <v>34</v>
@@ -3970,10 +4039,10 @@
         <v>11</v>
       </c>
       <c r="P11" t="s">
-        <v>27</v>
+        <v>116</v>
       </c>
       <c r="Q11">
-        <v>35</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12" spans="7:17" x14ac:dyDescent="0.25">
@@ -3984,53 +4053,47 @@
         <v>56</v>
       </c>
       <c r="J12" t="s">
-        <v>164</v>
+        <v>187</v>
       </c>
       <c r="K12">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="M12" t="s">
-        <v>165</v>
+        <v>188</v>
       </c>
       <c r="N12">
         <v>0</v>
       </c>
       <c r="P12" t="s">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="Q12">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="7:17" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G13" t="s">
-        <v>166</v>
+        <v>189</v>
       </c>
       <c r="H13">
         <v>0</v>
       </c>
       <c r="M13" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="N13">
         <v>7</v>
       </c>
-      <c r="P13" t="s">
-        <v>54</v>
-      </c>
-      <c r="Q13">
-        <v>1</v>
-      </c>
     </row>
     <row r="14" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G14" t="s">
-        <v>167</v>
+        <v>190</v>
       </c>
       <c r="H14">
         <v>0</v>
       </c>
       <c r="M14" t="s">
-        <v>153</v>
+        <v>176</v>
       </c>
       <c r="N14">
         <v>0</v>
@@ -4038,7 +4101,7 @@
     </row>
     <row r="15" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M15" t="s">
-        <v>168</v>
+        <v>191</v>
       </c>
       <c r="N15">
         <v>0</v>
@@ -4046,7 +4109,7 @@
     </row>
     <row r="16" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M16" t="s">
-        <v>169</v>
+        <v>192</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -4054,7 +4117,7 @@
     </row>
     <row r="17" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M17" t="s">
-        <v>170</v>
+        <v>193</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -4062,10 +4125,10 @@
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" s="6" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="20" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D20" s="1" t="s">
         <v>0</v>
       </c>
@@ -4073,7 +4136,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
@@ -4081,142 +4144,142 @@
     </row>
     <row r="21" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D21" s="2" t="s">
-        <v>67</v>
+        <v>29</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F21" s="2">
-        <v>495</v>
+        <v>614</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>69</v>
+        <v>31</v>
       </c>
     </row>
     <row r="22" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D22" s="2" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F22" s="2">
-        <v>0</v>
+        <v>614</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
     </row>
     <row r="23" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D23" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F23" s="2">
-        <v>0</v>
+        <v>614</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="24" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D24" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F24" s="2">
-        <v>0</v>
+        <v>614</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="25" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D25" s="2" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F25" s="2">
-        <v>0</v>
+        <v>614</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
     </row>
     <row r="26" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D26" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F26" s="2">
-        <v>0</v>
+        <v>614</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="27" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D27" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F27" s="2">
-        <v>0</v>
+        <v>614</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="28" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D28" s="2" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F28" s="2">
-        <v>0</v>
+        <v>614</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
     </row>
     <row r="29" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D29" s="2" t="s">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F29" s="2">
-        <v>0</v>
+        <v>614</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
     </row>
     <row r="30" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D30" s="2" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F30" s="2">
-        <v>0</v>
+        <v>614</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
